--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104577_W14.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104577_W14.xlsx
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.3734</v>
+        <v>2.6466</v>
       </c>
       <c r="E2" t="n">
-        <v>2.7083</v>
+        <v>3.8476</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.3349</v>
+        <v>-1.201</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4633</v>
+        <v>0.4514</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9538</v>
+        <v>0.9508</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.4905</v>
+        <v>-0.4994</v>
       </c>
       <c r="J2" t="n">
-        <v>3.4093</v>
+        <v>3.3612</v>
       </c>
       <c r="K2" t="n">
-        <v>2.8604</v>
+        <v>2.8334</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5489000000000001</v>
+        <v>0.5279</v>
       </c>
       <c r="M2" t="n">
-        <v>-2.946</v>
+        <v>-2.9098</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.9065</v>
+        <v>-1.8825</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.0395</v>
+        <v>-1.0273</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R2" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.368</v>
+        <v>-0.0732</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.1644</v>
+        <v>0.039</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2036</v>
+        <v>-0.1122</v>
       </c>
       <c r="V2" t="n">
-        <v>2.7317</v>
+        <v>2.7237</v>
       </c>
       <c r="W2" t="n">
-        <v>2.7317</v>
+        <v>2.7237</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -643,58 +643,58 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.7373</v>
+        <v>1.2507</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4628</v>
+        <v>0.9887</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2745</v>
+        <v>0.2621</v>
       </c>
       <c r="G3" t="n">
-        <v>1.1968</v>
+        <v>1.2006</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9942</v>
+        <v>0.9965000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2026</v>
+        <v>0.2041</v>
       </c>
       <c r="J3" t="n">
-        <v>2.0143</v>
+        <v>2.0015</v>
       </c>
       <c r="K3" t="n">
-        <v>1.42</v>
+        <v>1.4134</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5944</v>
+        <v>0.5881</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.8176</v>
+        <v>-0.8008999999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.4258</v>
+        <v>-0.4169</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.3918</v>
+        <v>-0.384</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.2326</v>
+        <v>0.2777</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.4174</v>
+        <v>0.1253</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1848</v>
+        <v>0.1524</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4499</v>
+        <v>-0.3214</v>
       </c>
       <c r="E4" t="n">
-        <v>3.0544</v>
+        <v>2.6548</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.6045</v>
+        <v>-2.9762</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.4462</v>
+        <v>-0.4573</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.3737</v>
+        <v>-1.3729</v>
       </c>
       <c r="I4" t="n">
-        <v>0.9275</v>
+        <v>0.9156</v>
       </c>
       <c r="J4" t="n">
-        <v>2.5666</v>
+        <v>2.525</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1865</v>
+        <v>0.1649</v>
       </c>
       <c r="L4" t="n">
-        <v>2.3802</v>
+        <v>2.3602</v>
       </c>
       <c r="M4" t="n">
-        <v>-3.0128</v>
+        <v>-2.9824</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.5602</v>
+        <v>-1.5378</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.4526</v>
+        <v>-1.4446</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R4" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8961</v>
+        <v>0.1359</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5293</v>
+        <v>0.1784</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3668</v>
+        <v>-0.0425</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>L. BOZIC</t>
+          <t>M. THOMAS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.6012999999999999</v>
+        <v>-1.4195</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.4623</v>
+        <v>1.4464</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.1391</v>
+        <v>-2.866</v>
       </c>
       <c r="G5" t="n">
-        <v>-3.8936</v>
+        <v>1.9545</v>
       </c>
       <c r="H5" t="n">
-        <v>-3.062</v>
+        <v>-1.9105</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.8317</v>
+        <v>3.865</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.5394</v>
+        <v>3.7921</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.825</v>
+        <v>-0.028</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.7144</v>
+        <v>3.8201</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.3542</v>
+        <v>-1.8376</v>
       </c>
       <c r="N5" t="n">
-        <v>-2.237</v>
+        <v>-1.8825</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.1172</v>
+        <v>0.0449</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.1342</v>
+        <v>-2.2763</v>
       </c>
       <c r="R5" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S5" t="n">
-        <v>3.0674</v>
+        <v>0.6456</v>
       </c>
       <c r="T5" t="n">
-        <v>2.0506</v>
+        <v>0.1599</v>
       </c>
       <c r="U5" t="n">
-        <v>1.0168</v>
+        <v>0.4857</v>
       </c>
       <c r="V5" t="n">
-        <v>0.2249</v>
+        <v>-2.8814</v>
       </c>
       <c r="W5" t="n">
-        <v>0.1607</v>
+        <v>-0.2292</v>
       </c>
       <c r="X5" t="n">
-        <v>0.06419999999999999</v>
+        <v>-2.6522</v>
       </c>
     </row>
     <row r="6">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.4877</v>
+        <v>-1.435</v>
       </c>
       <c r="E6" t="n">
-        <v>1.244</v>
+        <v>0.9863</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.7316</v>
+        <v>-2.4213</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7554999999999999</v>
+        <v>0.7623</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.1156</v>
+        <v>-1.1008</v>
       </c>
       <c r="I6" t="n">
-        <v>1.8711</v>
+        <v>1.8632</v>
       </c>
       <c r="J6" t="n">
-        <v>2.468</v>
+        <v>2.4568</v>
       </c>
       <c r="K6" t="n">
-        <v>0.381</v>
+        <v>0.3792</v>
       </c>
       <c r="L6" t="n">
-        <v>2.087</v>
+        <v>2.0776</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.7125</v>
+        <v>-1.6945</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.4966</v>
+        <v>-1.48</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.2159</v>
+        <v>-0.2144</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1751</v>
+        <v>-0.129</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0484</v>
+        <v>-0.2837</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1267</v>
+        <v>0.1546</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.7071</v>
+        <v>-0.7025</v>
       </c>
       <c r="W6" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.7997</v>
+        <v>-1.792</v>
       </c>
     </row>
     <row r="7">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.941</v>
+        <v>-2.0471</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.5387</v>
+        <v>-0.7161999999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.4022</v>
+        <v>-1.3309</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.4992</v>
+        <v>-1.4964</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.5743</v>
+        <v>-0.5744</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.9249000000000001</v>
+        <v>-0.9219000000000001</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.143</v>
+        <v>-0.1491</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.1803</v>
+        <v>-0.1864</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.3563</v>
+        <v>-1.3472</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.394</v>
+        <v>-0.3881</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.9622000000000001</v>
+        <v>-0.9592000000000001</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R7" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3049</v>
+        <v>0.202</v>
       </c>
       <c r="T7" t="n">
-        <v>0.5777</v>
+        <v>0.4133</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2728</v>
+        <v>-0.2113</v>
       </c>
       <c r="V7" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="W7" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>B. OLUMUYIWA</t>
+          <t>L. BOZIC</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.9694</v>
+        <v>-2.0798</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.5272</v>
+        <v>-1.605</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.4422</v>
+        <v>-0.4748</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.5175</v>
+        <v>-3.8975</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.4025</v>
+        <v>-3.0617</v>
       </c>
       <c r="I8" t="n">
-        <v>0.885</v>
+        <v>-0.8359</v>
       </c>
       <c r="J8" t="n">
-        <v>0.4235</v>
+        <v>-1.5717</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.3228</v>
+        <v>-0.8488</v>
       </c>
       <c r="L8" t="n">
-        <v>0.7463</v>
+        <v>-0.7228</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.941</v>
+        <v>-2.3258</v>
       </c>
       <c r="N8" t="n">
-        <v>-2.0797</v>
+        <v>-2.2128</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1387</v>
+        <v>-0.113</v>
       </c>
       <c r="P8" t="n">
-        <v>0.4537</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5878</v>
+        <v>1.1382</v>
       </c>
       <c r="S8" t="n">
-        <v>1.119</v>
+        <v>1.5885</v>
       </c>
       <c r="T8" t="n">
-        <v>0.4083</v>
+        <v>0.9471000000000001</v>
       </c>
       <c r="U8" t="n">
-        <v>0.7107</v>
+        <v>0.6415</v>
       </c>
       <c r="V8" t="n">
-        <v>-2.0246</v>
+        <v>0.2292</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.2249</v>
+        <v>0.1578</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.7997</v>
+        <v>0.07140000000000001</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. THOMAS</t>
+          <t>B. OLUMUYIWA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.1217</v>
+        <v>-2.3588</v>
       </c>
       <c r="E9" t="n">
-        <v>1.231</v>
+        <v>-0.9628</v>
       </c>
       <c r="F9" t="n">
-        <v>-3.3527</v>
+        <v>-1.396</v>
       </c>
       <c r="G9" t="n">
-        <v>1.9575</v>
+        <v>-1.5128</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.9207</v>
+        <v>-2.4039</v>
       </c>
       <c r="I9" t="n">
-        <v>3.8782</v>
+        <v>0.8911</v>
       </c>
       <c r="J9" t="n">
-        <v>3.824</v>
+        <v>0.3958</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.0142</v>
+        <v>-0.349</v>
       </c>
       <c r="L9" t="n">
-        <v>3.8382</v>
+        <v>0.7447</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.8665</v>
+        <v>-1.9086</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.9065</v>
+        <v>-2.0549</v>
       </c>
       <c r="O9" t="n">
-        <v>0.04</v>
+        <v>0.1463</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.1342</v>
+        <v>0.4553</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.2683</v>
+        <v>-1.1382</v>
       </c>
       <c r="R9" t="n">
-        <v>1.1342</v>
+        <v>1.5934</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0526</v>
+        <v>0.7199</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0998</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0472</v>
+        <v>0.7112000000000001</v>
       </c>
       <c r="V9" t="n">
-        <v>-2.8924</v>
+        <v>-2.0212</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.2249</v>
+        <v>-0.2292</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.6675</v>
+        <v>-1.792</v>
       </c>
     </row>
     <row r="10">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.1134</v>
+        <v>-4.7892</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.6575</v>
+        <v>-3.3186</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.4559</v>
+        <v>-1.4706</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.6634</v>
+        <v>-2.6582</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.8082</v>
+        <v>-0.7989000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.8552</v>
+        <v>-1.8592</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.1291</v>
+        <v>-1.1373</v>
       </c>
       <c r="K10" t="n">
-        <v>0.2944</v>
+        <v>0.293</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.4234</v>
+        <v>-1.4303</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.5344</v>
+        <v>-1.5209</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.1026</v>
+        <v>-1.092</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.4318</v>
+        <v>-0.4289</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0209</v>
+        <v>0.3031</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2601</v>
+        <v>0.095</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2392</v>
+        <v>0.208</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-7.9028</v>
+        <v>-7.3256</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.641</v>
+        <v>-4.0708</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.2618</v>
+        <v>-3.2549</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.4117</v>
+        <v>-3.4142</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.7084</v>
+        <v>-1.7116</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.7033</v>
+        <v>-1.7026</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.4965</v>
+        <v>-1.5226</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.5581</v>
+        <v>-0.5763</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.9383</v>
+        <v>-0.9463</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.9152</v>
+        <v>-1.8916</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.1503</v>
+        <v>-1.1353</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.7649</v>
+        <v>-0.7563</v>
       </c>
       <c r="P11" t="n">
-        <v>-2.0415</v>
+        <v>-2.0487</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R11" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.65</v>
+        <v>-0.0708</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.8347</v>
+        <v>-0.2232</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1848</v>
+        <v>0.1524</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.7997</v>
+        <v>-1.792</v>
       </c>
       <c r="W11" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.8924</v>
+        <v>-2.8814</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-18.5767</v>
+        <v>-17.8791</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.1262</v>
+        <v>-0.7496</v>
       </c>
       <c r="F12" t="n">
-        <v>-17.4504</v>
+        <v>-17.1296</v>
       </c>
       <c r="G12" t="n">
-        <v>-9.0585</v>
+        <v>-9.067599999999999</v>
       </c>
       <c r="H12" t="n">
-        <v>-11.0174</v>
+        <v>-10.9874</v>
       </c>
       <c r="I12" t="n">
-        <v>1.958800000000001</v>
+        <v>1.92</v>
       </c>
       <c r="J12" t="n">
-        <v>10.3977</v>
+        <v>10.1517</v>
       </c>
       <c r="K12" t="n">
-        <v>3.2419</v>
+        <v>3.095400000000001</v>
       </c>
       <c r="L12" t="n">
-        <v>7.1562</v>
+        <v>7.056400000000001</v>
       </c>
       <c r="M12" t="n">
-        <v>-19.4565</v>
+        <v>-19.2193</v>
       </c>
       <c r="N12" t="n">
-        <v>-14.2592</v>
+        <v>-14.0828</v>
       </c>
       <c r="O12" t="n">
-        <v>-5.1972</v>
+        <v>-5.1365</v>
       </c>
       <c r="P12" t="n">
-        <v>-7.939100000000001</v>
+        <v>-7.9671</v>
       </c>
       <c r="Q12" t="n">
-        <v>-18.1467</v>
+        <v>-18.2107</v>
       </c>
       <c r="R12" t="n">
-        <v>10.2075</v>
+        <v>10.2435</v>
       </c>
       <c r="S12" t="n">
-        <v>2.8882</v>
+        <v>3.5997</v>
       </c>
       <c r="T12" t="n">
-        <v>0.7411000000000001</v>
+        <v>1.4599</v>
       </c>
       <c r="U12" t="n">
-        <v>2.1472</v>
+        <v>2.1398</v>
       </c>
       <c r="V12" t="n">
-        <v>-4.4672</v>
+        <v>-4.444199999999999</v>
       </c>
       <c r="W12" t="n">
-        <v>5.8814</v>
+        <v>5.8494</v>
       </c>
       <c r="X12" t="n">
-        <v>-10.3485</v>
+        <v>-10.2935</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>7.8315</v>
+        <v>8.395099999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>6.6966</v>
+        <v>6.9994</v>
       </c>
       <c r="F13" t="n">
-        <v>1.135</v>
+        <v>1.3957</v>
       </c>
       <c r="G13" t="n">
-        <v>5.0113</v>
+        <v>5.0082</v>
       </c>
       <c r="H13" t="n">
-        <v>4.0836</v>
+        <v>4.0786</v>
       </c>
       <c r="I13" t="n">
-        <v>0.9276</v>
+        <v>0.9296</v>
       </c>
       <c r="J13" t="n">
-        <v>5.6601</v>
+        <v>5.6204</v>
       </c>
       <c r="K13" t="n">
-        <v>4.3221</v>
+        <v>4.2952</v>
       </c>
       <c r="L13" t="n">
-        <v>1.338</v>
+        <v>1.3252</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.6488</v>
+        <v>-0.6122</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.2384</v>
+        <v>-0.2166</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.4104</v>
+        <v>-0.3956</v>
       </c>
       <c r="P13" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.1136</v>
+        <v>-0.5432</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.5383</v>
+        <v>-0.1838</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.5753</v>
+        <v>-0.3595</v>
       </c>
       <c r="V13" t="n">
-        <v>2.3461</v>
+        <v>2.3367</v>
       </c>
       <c r="W13" t="n">
-        <v>1.5748</v>
+        <v>1.5628</v>
       </c>
       <c r="X13" t="n">
-        <v>0.7712</v>
+        <v>0.7739</v>
       </c>
     </row>
     <row r="14">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.9285</v>
+        <v>4.1234</v>
       </c>
       <c r="E14" t="n">
-        <v>2.773</v>
+        <v>2.6079</v>
       </c>
       <c r="F14" t="n">
-        <v>1.1556</v>
+        <v>1.5155</v>
       </c>
       <c r="G14" t="n">
-        <v>1.6993</v>
+        <v>1.7048</v>
       </c>
       <c r="H14" t="n">
-        <v>0.8917</v>
+        <v>0.8959</v>
       </c>
       <c r="I14" t="n">
-        <v>0.8077</v>
+        <v>0.8089</v>
       </c>
       <c r="J14" t="n">
-        <v>2.5213</v>
+        <v>2.4893</v>
       </c>
       <c r="K14" t="n">
-        <v>1.146</v>
+        <v>1.1269</v>
       </c>
       <c r="L14" t="n">
-        <v>1.3753</v>
+        <v>1.3624</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.822</v>
+        <v>-0.7846</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.2543</v>
+        <v>-0.231</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.5676</v>
+        <v>-0.5535</v>
       </c>
       <c r="P14" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R14" t="n">
-        <v>2.4952</v>
+        <v>2.5039</v>
       </c>
       <c r="S14" t="n">
-        <v>0.2253</v>
+        <v>0.4218</v>
       </c>
       <c r="T14" t="n">
-        <v>0.1966</v>
+        <v>0.0809</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0287</v>
+        <v>0.3408</v>
       </c>
       <c r="V14" t="n">
-        <v>0.6429</v>
+        <v>0.6311</v>
       </c>
       <c r="W14" t="n">
-        <v>1.1892</v>
+        <v>1.1758</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>L. FISCHER</t>
+          <t>J. JACKSON</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.5265</v>
+        <v>2.5903</v>
       </c>
       <c r="E15" t="n">
-        <v>1.7048</v>
+        <v>2.3672</v>
       </c>
       <c r="F15" t="n">
-        <v>1.8216</v>
+        <v>0.2231</v>
       </c>
       <c r="G15" t="n">
-        <v>2.0425</v>
+        <v>-0.8988</v>
       </c>
       <c r="H15" t="n">
-        <v>0.8269</v>
+        <v>-1.0594</v>
       </c>
       <c r="I15" t="n">
-        <v>1.2156</v>
+        <v>0.1606</v>
       </c>
       <c r="J15" t="n">
-        <v>0.5728</v>
+        <v>1.293</v>
       </c>
       <c r="K15" t="n">
-        <v>0.4982</v>
+        <v>-0.628</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0746</v>
+        <v>1.921</v>
       </c>
       <c r="M15" t="n">
-        <v>1.4697</v>
+        <v>-2.1918</v>
       </c>
       <c r="N15" t="n">
-        <v>0.3288</v>
+        <v>-0.4314</v>
       </c>
       <c r="O15" t="n">
-        <v>1.1409</v>
+        <v>-1.7604</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.2268</v>
+        <v>0.6829</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R15" t="n">
-        <v>0.9073</v>
+        <v>1.8211</v>
       </c>
       <c r="S15" t="n">
-        <v>1.8715</v>
+        <v>-0.3044</v>
       </c>
       <c r="T15" t="n">
-        <v>1.1735</v>
+        <v>-0.5113</v>
       </c>
       <c r="U15" t="n">
-        <v>0.698</v>
+        <v>0.2069</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.1607</v>
+        <v>3.1107</v>
       </c>
       <c r="W15" t="n">
-        <v>1.0927</v>
+        <v>2.7237</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.2534</v>
+        <v>0.387</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. JACKSON</t>
+          <t>L. FISCHER</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.3114</v>
+        <v>2.4554</v>
       </c>
       <c r="E16" t="n">
-        <v>2.1755</v>
+        <v>0.8514</v>
       </c>
       <c r="F16" t="n">
-        <v>0.1359</v>
+        <v>1.604</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.8839</v>
+        <v>2.0439</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.0518</v>
+        <v>0.819</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1679</v>
+        <v>1.2249</v>
       </c>
       <c r="J16" t="n">
-        <v>1.325</v>
+        <v>0.5496</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.6101</v>
+        <v>0.4752</v>
       </c>
       <c r="L16" t="n">
-        <v>1.9351</v>
+        <v>0.0745</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.2089</v>
+        <v>1.4942</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.4417</v>
+        <v>0.3438</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.7672</v>
+        <v>1.1504</v>
       </c>
       <c r="P16" t="n">
-        <v>0.6805</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R16" t="n">
-        <v>1.8147</v>
+        <v>0.9105</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.6025</v>
+        <v>0.797</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.747</v>
+        <v>0.3505</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1446</v>
+        <v>0.4465</v>
       </c>
       <c r="V16" t="n">
-        <v>3.1173</v>
+        <v>-0.1578</v>
       </c>
       <c r="W16" t="n">
-        <v>2.7317</v>
+        <v>1.0895</v>
       </c>
       <c r="X16" t="n">
-        <v>0.3856</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="17">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.8589</v>
+        <v>1.5406</v>
       </c>
       <c r="E17" t="n">
-        <v>3.2876</v>
+        <v>3.021</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.4288</v>
+        <v>-1.4804</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.4164</v>
+        <v>-0.4117</v>
       </c>
       <c r="H17" t="n">
-        <v>0.8096</v>
+        <v>0.8017</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.226</v>
+        <v>-1.2135</v>
       </c>
       <c r="J17" t="n">
-        <v>2.8392</v>
+        <v>2.8127</v>
       </c>
       <c r="K17" t="n">
-        <v>2.6526</v>
+        <v>2.6265</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1866</v>
+        <v>0.1862</v>
       </c>
       <c r="M17" t="n">
-        <v>-3.2556</v>
+        <v>-3.2244</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.8429</v>
+        <v>-1.8248</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.4126</v>
+        <v>-1.3997</v>
       </c>
       <c r="P17" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S17" t="n">
-        <v>0.2338</v>
+        <v>-0.0964</v>
       </c>
       <c r="T17" t="n">
-        <v>0.127</v>
+        <v>-0.1072</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1067</v>
+        <v>0.0108</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>0.3214</v>
+        <v>0.3155</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.3214</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="18">
@@ -1813,58 +1813,58 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.235</v>
+        <v>1.1161</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.2012</v>
+        <v>-0.2023</v>
       </c>
       <c r="F18" t="n">
-        <v>1.4363</v>
+        <v>1.3184</v>
       </c>
       <c r="G18" t="n">
-        <v>0.1148</v>
+        <v>0.1173</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.1544</v>
+        <v>-0.1523</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2692</v>
+        <v>0.2696</v>
       </c>
       <c r="J18" t="n">
-        <v>0.1466</v>
+        <v>0.1462</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0346</v>
+        <v>0.0345</v>
       </c>
       <c r="L18" t="n">
-        <v>0.112</v>
+        <v>0.1117</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.0318</v>
+        <v>-0.0289</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.1891</v>
+        <v>-0.1868</v>
       </c>
       <c r="O18" t="n">
-        <v>0.1573</v>
+        <v>0.1579</v>
       </c>
       <c r="P18" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2407</v>
+        <v>-0.367</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3478</v>
+        <v>-0.3485</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1071</v>
+        <v>-0.0185</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,58 +1891,58 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.7036</v>
+        <v>0.7745</v>
       </c>
       <c r="E19" t="n">
-        <v>0.2783</v>
+        <v>0.2748</v>
       </c>
       <c r="F19" t="n">
-        <v>0.4253</v>
+        <v>0.4997</v>
       </c>
       <c r="G19" t="n">
-        <v>0.2611</v>
+        <v>0.2669</v>
       </c>
       <c r="H19" t="n">
-        <v>0.8715000000000001</v>
+        <v>0.873</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.6104000000000001</v>
+        <v>-0.6061</v>
       </c>
       <c r="J19" t="n">
-        <v>0.6261</v>
+        <v>0.6233</v>
       </c>
       <c r="K19" t="n">
-        <v>0.5888</v>
+        <v>0.5861</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.3649</v>
+        <v>-0.3563</v>
       </c>
       <c r="N19" t="n">
-        <v>0.2828</v>
+        <v>0.287</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.6477000000000001</v>
+        <v>-0.6433</v>
       </c>
       <c r="P19" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4649</v>
+        <v>-0.403</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3478</v>
+        <v>-0.3485</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1171</v>
+        <v>-0.0545</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0123</v>
+        <v>0.6139</v>
       </c>
       <c r="E20" t="n">
-        <v>1.2873</v>
+        <v>1.7284</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.275</v>
+        <v>-1.1145</v>
       </c>
       <c r="G20" t="n">
-        <v>0.2252</v>
+        <v>0.2283</v>
       </c>
       <c r="H20" t="n">
-        <v>1.414</v>
+        <v>1.4186</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.1888</v>
+        <v>-1.1903</v>
       </c>
       <c r="J20" t="n">
-        <v>2.1272</v>
+        <v>2.1027</v>
       </c>
       <c r="K20" t="n">
-        <v>2.0607</v>
+        <v>2.0512</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0665</v>
+        <v>0.0515</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.902</v>
+        <v>-1.8744</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.6467000000000001</v>
+        <v>-0.6326000000000001</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.2554</v>
+        <v>-1.2417</v>
       </c>
       <c r="P20" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R20" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.8934</v>
+        <v>-0.2973</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.7984</v>
+        <v>-0.3256</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.095</v>
+        <v>0.0283</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="21">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.0289</v>
+        <v>-0.2412</v>
       </c>
       <c r="E21" t="n">
-        <v>0.3082</v>
+        <v>0.7327</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.3371</v>
+        <v>-0.974</v>
       </c>
       <c r="G21" t="n">
-        <v>1.4742</v>
+        <v>1.479</v>
       </c>
       <c r="H21" t="n">
-        <v>3.1934</v>
+        <v>3.1856</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.7192</v>
+        <v>-1.7065</v>
       </c>
       <c r="J21" t="n">
-        <v>3.4826</v>
+        <v>3.4532</v>
       </c>
       <c r="K21" t="n">
-        <v>3.2587</v>
+        <v>3.2298</v>
       </c>
       <c r="L21" t="n">
-        <v>0.2239</v>
+        <v>0.2234</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.0083</v>
+        <v>-1.9742</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.0653</v>
+        <v>-0.0442</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.9431</v>
+        <v>-1.93</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R21" t="n">
-        <v>3.4025</v>
+        <v>3.4145</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.5712</v>
+        <v>-0.7885</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.0253</v>
+        <v>-0.5532</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.5459000000000001</v>
+        <v>-0.2353</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.9320000000000001</v>
+        <v>-0.9317</v>
       </c>
       <c r="W21" t="n">
-        <v>1.2534</v>
+        <v>1.2472</v>
       </c>
       <c r="X21" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="22">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.8022</v>
+        <v>-2.0022</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.9523</v>
+        <v>-2.3404</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1501</v>
+        <v>0.3382</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.4695</v>
+        <v>-0.4704</v>
       </c>
       <c r="H22" t="n">
-        <v>0.1329</v>
+        <v>0.1267</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.6024</v>
+        <v>-0.5971</v>
       </c>
       <c r="J22" t="n">
-        <v>0.1557</v>
+        <v>0.1289</v>
       </c>
       <c r="K22" t="n">
-        <v>0.3077</v>
+        <v>0.2855</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.152</v>
+        <v>-0.1566</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.6252</v>
+        <v>-0.5993000000000001</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.1749</v>
+        <v>-0.1588</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.4504</v>
+        <v>-0.4405</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R22" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3327</v>
+        <v>-0.5318000000000001</v>
       </c>
       <c r="T22" t="n">
-        <v>0.1603</v>
+        <v>-0.193</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.493</v>
+        <v>-0.3388</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="23">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>18.5766</v>
+        <v>19.3659</v>
       </c>
       <c r="E23" t="n">
-        <v>16.3578</v>
+        <v>16.0401</v>
       </c>
       <c r="F23" t="n">
-        <v>2.2189</v>
+        <v>3.325700000000001</v>
       </c>
       <c r="G23" t="n">
-        <v>9.0586</v>
+        <v>9.067500000000001</v>
       </c>
       <c r="H23" t="n">
-        <v>11.0174</v>
+        <v>10.9874</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.9588</v>
+        <v>-1.919899999999999</v>
       </c>
       <c r="J23" t="n">
-        <v>19.4566</v>
+        <v>19.2193</v>
       </c>
       <c r="K23" t="n">
-        <v>14.2593</v>
+        <v>14.0829</v>
       </c>
       <c r="L23" t="n">
-        <v>5.197300000000001</v>
+        <v>5.136499999999999</v>
       </c>
       <c r="M23" t="n">
-        <v>-10.3978</v>
+        <v>-10.1519</v>
       </c>
       <c r="N23" t="n">
-        <v>-3.2417</v>
+        <v>-3.0954</v>
       </c>
       <c r="O23" t="n">
-        <v>-7.156200000000001</v>
+        <v>-7.0564</v>
       </c>
       <c r="P23" t="n">
-        <v>7.9391</v>
+        <v>7.967099999999999</v>
       </c>
       <c r="Q23" t="n">
-        <v>-10.2076</v>
+        <v>-10.2436</v>
       </c>
       <c r="R23" t="n">
-        <v>18.1467</v>
+        <v>18.2106</v>
       </c>
       <c r="S23" t="n">
-        <v>-2.8884</v>
+        <v>-2.1128</v>
       </c>
       <c r="T23" t="n">
-        <v>-2.1472</v>
+        <v>-2.1397</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.7412000000000001</v>
+        <v>0.0267</v>
       </c>
       <c r="V23" t="n">
-        <v>4.4673</v>
+        <v>4.4443</v>
       </c>
       <c r="W23" t="n">
-        <v>9.2559</v>
+        <v>9.203999999999999</v>
       </c>
       <c r="X23" t="n">
-        <v>-4.788600000000001</v>
+        <v>-4.7596</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104577_W14.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104577_W14.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X23"/>
+  <dimension ref="A1:Y23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104577_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104577_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104577_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-2.6522</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104577_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-1.792</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104577_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104577_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0.07140000000000001</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104577_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-1.792</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104577_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104577_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-2.8814</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104577_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,7 @@
       <c r="X12" t="n">
         <v>-10.2935</v>
       </c>
+      <c r="Y12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1541,11 @@
       <c r="X13" t="n">
         <v>0.7739</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104577_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104577_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>0.387</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104577_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104577_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104577_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>0</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104577_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>0</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104577_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104577_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104577_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104577_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,7 @@
       <c r="X23" t="n">
         <v>-4.7596</v>
       </c>
+      <c r="Y23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
